--- a/e_commerce_forms/001_fall_pre_order--e_commerce_forms.xlsx
+++ b/e_commerce_forms/001_fall_pre_order--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,69 +515,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fall_preorder</t>
+          <t>product_preorder</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>What is the product being preordered?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>How many would you like to preorder?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>How would you like to be contacted?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,19 +589,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>other_products</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter email</t>
-        </is>
-      </c>
+          <t>Are you interested in other products?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -616,35 +612,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fall_preorder</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Do you have any other comments or questions?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>updates</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Would you like to receive updates on this preorder?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,20 +681,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>add_other_products</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter email</t>
-        </is>
-      </c>
+          <t>Would you like to add any other products to your preorder?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>email_confirmation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Please confirm your email address</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Do you have any additional comments?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>confirm_updates</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Would you like to confirm you want to receive updates?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>additional_products</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Add any other products to your preorder</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -718,9 +802,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,102 +827,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>product_preorder_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>product_1</t>
+          <t>fleece_jacket</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product 1</t>
+          <t>Fleece Jacket</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>product_preorder_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>product_2</t>
+          <t>hoodie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Product 2</t>
+          <t>Hoodie</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>product_preorder_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>product_3</t>
+          <t>sweater</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Product 3</t>
+          <t>Sweater</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>product_1</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Product 1</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>product_2</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Product 2</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>product_3</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Product 3</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
